--- a/Monthly_Retention.xlsx
+++ b/Monthly_Retention.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="34">
   <si>
     <t>Reg. Month</t>
   </si>
@@ -78,7 +78,7 @@
     <t>Old</t>
   </si>
   <si>
-    <t>Old /</t>
+    <t>Users %</t>
   </si>
   <si>
     <t>New Users</t>
@@ -87,7 +87,7 @@
     <t>Old Users</t>
   </si>
   <si>
-    <t>New Revenue</t>
+    <t>Revenue %</t>
   </si>
   <si>
     <t>RPU</t>
@@ -138,40 +138,25 @@
     <t>Txn. Month</t>
   </si>
   <si>
-    <t>Total Users</t>
+    <t>Total Users \ Age-&gt;</t>
   </si>
   <si>
-    <t>M0 Users</t>
+    <t>Same Month</t>
   </si>
   <si>
-    <t>M1 Users</t>
+    <t>1 Month Old</t>
   </si>
   <si>
-    <t>M2 Users</t>
+    <t>2 Months Old</t>
   </si>
   <si>
-    <t>M3-M5 Users</t>
+    <t>3-5 Months Old</t>
   </si>
   <si>
-    <t>M6-M11 Users</t>
+    <t>6-11 Months Old</t>
   </si>
   <si>
-    <t>Total Rev.</t>
-  </si>
-  <si>
-    <t>M0 Revenue</t>
-  </si>
-  <si>
-    <t>M1 Revenue</t>
-  </si>
-  <si>
-    <t>M2 Revenue</t>
-  </si>
-  <si>
-    <t>M3-M5 Rev.</t>
-  </si>
-  <si>
-    <t>M6-M11 Rev.</t>
+    <t>Total Rev. \ Age-&gt;</t>
   </si>
 </sst>
 </file>
@@ -909,7 +894,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -925,122 +910,125 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="2" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="2" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="2" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="2" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="2" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="2" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="2" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="2" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="2" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="2" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="2" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="2" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="2" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="2" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2581,109 +2569,109 @@
       <c r="B31" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="44">
         <f ca="1" t="shared" ref="C31:N31" si="3">C28-C30</f>
         <v>0</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="44">
         <f ca="1" t="shared" si="3"/>
         <v>1404</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="44">
         <f ca="1" t="shared" si="3"/>
         <v>2567</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="44">
         <f ca="1" t="shared" si="3"/>
         <v>3622</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="44">
         <f ca="1" t="shared" si="3"/>
         <v>3335</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="44">
         <f ca="1" t="shared" si="3"/>
         <v>3730</v>
       </c>
-      <c r="I31" s="7">
+      <c r="I31" s="44">
         <f ca="1" t="shared" si="3"/>
         <v>3766</v>
       </c>
-      <c r="J31" s="7">
+      <c r="J31" s="44">
         <f ca="1" t="shared" si="3"/>
         <v>3128</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K31" s="44">
         <f ca="1" t="shared" si="3"/>
         <v>3597</v>
       </c>
-      <c r="L31" s="7">
+      <c r="L31" s="44">
         <f ca="1" t="shared" si="3"/>
         <v>3173</v>
       </c>
-      <c r="M31" s="7">
+      <c r="M31" s="44">
         <f ca="1" t="shared" si="3"/>
         <v>3308</v>
       </c>
-      <c r="N31" s="44">
+      <c r="N31" s="45">
         <f ca="1" t="shared" si="3"/>
         <v>3227</v>
       </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="39" t="s">
+      <c r="A32" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="45">
-        <f ca="1" t="shared" ref="C32:N32" si="4">C31/C30</f>
+      <c r="C32" s="46">
+        <f ca="1" t="shared" ref="C32:N32" si="4">C31/C28</f>
         <v>0</v>
       </c>
-      <c r="D32" s="45">
+      <c r="D32" s="46">
         <f ca="1" t="shared" si="4"/>
-        <v>0.0877609701212652</v>
-      </c>
-      <c r="E32" s="45">
+        <v>0.0806803815653373</v>
+      </c>
+      <c r="E32" s="46">
         <f ca="1" t="shared" si="4"/>
-        <v>0.13406800020891</v>
-      </c>
-      <c r="F32" s="45">
+        <v>0.118218660771852</v>
+      </c>
+      <c r="F32" s="46">
         <f ca="1" t="shared" si="4"/>
-        <v>0.187086776859504</v>
-      </c>
-      <c r="G32" s="45">
+        <v>0.157601601253155</v>
+      </c>
+      <c r="G32" s="46">
         <f ca="1" t="shared" si="4"/>
-        <v>0.179445789615281</v>
-      </c>
-      <c r="H32" s="45">
+        <v>0.152144160583942</v>
+      </c>
+      <c r="H32" s="46">
         <f ca="1" t="shared" si="4"/>
-        <v>0.270839384257915</v>
-      </c>
-      <c r="I32" s="45">
+        <v>0.213118500742772</v>
+      </c>
+      <c r="I32" s="46">
         <f ca="1" t="shared" si="4"/>
-        <v>0.35686534634701</v>
-      </c>
-      <c r="J32" s="45">
+        <v>0.263007193239751</v>
+      </c>
+      <c r="J32" s="46">
         <f ca="1" t="shared" si="4"/>
-        <v>0.24182450715114</v>
-      </c>
-      <c r="K32" s="45">
+        <v>0.194733237875864</v>
+      </c>
+      <c r="K32" s="46">
         <f ca="1" t="shared" si="4"/>
-        <v>0.327089206147131</v>
-      </c>
-      <c r="L32" s="45">
+        <v>0.246471152528436</v>
+      </c>
+      <c r="L32" s="46">
         <f ca="1" t="shared" si="4"/>
-        <v>0.271266136616226</v>
-      </c>
-      <c r="M32" s="45">
+        <v>0.213382649630128</v>
+      </c>
+      <c r="M32" s="46">
         <f ca="1" t="shared" si="4"/>
-        <v>0.28215626066189</v>
-      </c>
-      <c r="N32" s="46">
+        <v>0.220063863757318</v>
+      </c>
+      <c r="N32" s="47">
         <f ca="1" t="shared" si="4"/>
-        <v>0.224362094138914</v>
+        <v>0.183248154457694</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -2752,109 +2740,109 @@
       <c r="B35" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="44">
         <f ca="1" t="shared" ref="C35:N35" si="6">C27-C34</f>
         <v>0</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="44">
         <f ca="1" t="shared" si="6"/>
         <v>4531845.6734533</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="44">
         <f ca="1" t="shared" si="6"/>
         <v>5267754.15098363</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="44">
         <f ca="1" t="shared" si="6"/>
         <v>6162341.16088317</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="44">
         <f ca="1" t="shared" si="6"/>
         <v>8942618.21220937</v>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="44">
         <f ca="1" t="shared" si="6"/>
         <v>8317457.95105369</v>
       </c>
-      <c r="I35" s="7">
+      <c r="I35" s="44">
         <f ca="1" t="shared" si="6"/>
         <v>8048223.23120195</v>
       </c>
-      <c r="J35" s="7">
+      <c r="J35" s="44">
         <f ca="1" t="shared" si="6"/>
         <v>10148336.7429296</v>
       </c>
-      <c r="K35" s="7">
+      <c r="K35" s="44">
         <f ca="1" t="shared" si="6"/>
         <v>12505756.7243128</v>
       </c>
-      <c r="L35" s="7">
+      <c r="L35" s="44">
         <f ca="1" t="shared" si="6"/>
         <v>15252113.9431369</v>
       </c>
-      <c r="M35" s="7">
+      <c r="M35" s="44">
         <f ca="1" t="shared" si="6"/>
         <v>15173517.9731045</v>
       </c>
-      <c r="N35" s="44">
+      <c r="N35" s="45">
         <f ca="1" t="shared" si="6"/>
         <v>22310246.2428781</v>
       </c>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="32" t="s">
+      <c r="A36" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C36" s="45">
-        <f ca="1" t="shared" ref="C36:N36" si="7">C35/C34</f>
+      <c r="C36" s="46">
+        <f ca="1">C35/C27</f>
         <v>0</v>
       </c>
-      <c r="D36" s="45">
+      <c r="D36" s="46">
+        <f ca="1" t="shared" ref="C36:N36" si="7">D35/D27</f>
+        <v>0.469535004138121</v>
+      </c>
+      <c r="E36" s="46">
         <f ca="1" t="shared" si="7"/>
-        <v>0.8851385252579</v>
-      </c>
-      <c r="E36" s="45">
+        <v>0.579950534351628</v>
+      </c>
+      <c r="F36" s="46">
         <f ca="1" t="shared" si="7"/>
-        <v>1.38067199646698</v>
-      </c>
-      <c r="F36" s="45">
+        <v>0.575369639736814</v>
+      </c>
+      <c r="G36" s="46">
         <f ca="1" t="shared" si="7"/>
-        <v>1.35498940626902</v>
-      </c>
-      <c r="G36" s="45">
+        <v>0.754702801544942</v>
+      </c>
+      <c r="H36" s="46">
         <f ca="1" t="shared" si="7"/>
-        <v>3.07668740735012</v>
-      </c>
-      <c r="H36" s="45">
+        <v>0.792459318323716</v>
+      </c>
+      <c r="I36" s="46">
         <f ca="1" t="shared" si="7"/>
-        <v>3.81833244414111</v>
-      </c>
-      <c r="I36" s="45">
+        <v>0.735499065483886</v>
+      </c>
+      <c r="J36" s="46">
         <f ca="1" t="shared" si="7"/>
-        <v>2.78070497871559</v>
-      </c>
-      <c r="J36" s="45">
+        <v>0.75729005370212</v>
+      </c>
+      <c r="K36" s="46">
         <f ca="1" t="shared" si="7"/>
-        <v>3.12014429261457</v>
-      </c>
-      <c r="K36" s="45">
+        <v>0.819569707349506</v>
+      </c>
+      <c r="L36" s="46">
         <f ca="1" t="shared" si="7"/>
-        <v>4.54230659004179</v>
-      </c>
-      <c r="L36" s="45">
+        <v>0.83450941398942</v>
+      </c>
+      <c r="M36" s="46">
         <f ca="1" t="shared" si="7"/>
-        <v>5.04263979061667</v>
-      </c>
-      <c r="M36" s="45">
+        <v>0.811403349647317</v>
+      </c>
+      <c r="N36" s="47">
         <f ca="1" t="shared" si="7"/>
-        <v>4.30232110766528</v>
-      </c>
-      <c r="N36" s="46">
-        <f ca="1" t="shared" si="7"/>
-        <v>8.17988643826338</v>
+        <v>0.891066190554185</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2923,51 +2911,51 @@
       <c r="B39" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="44">
         <f ca="1">IFERROR(C35/C31,0)</f>
         <v>0</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="44">
         <f ca="1" t="shared" ref="C39:N39" si="9">D35/D31</f>
         <v>3227.81030872742</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="44">
         <f ca="1" t="shared" si="9"/>
         <v>2052.10523996246</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="44">
         <f ca="1" t="shared" si="9"/>
         <v>1701.36420786393</v>
       </c>
-      <c r="G39" s="7">
+      <c r="G39" s="44">
         <f ca="1" t="shared" si="9"/>
         <v>2681.44474129216</v>
       </c>
-      <c r="H39" s="7">
+      <c r="H39" s="44">
         <f ca="1" t="shared" si="9"/>
         <v>2229.88148821815</v>
       </c>
-      <c r="I39" s="7">
+      <c r="I39" s="44">
         <f ca="1" t="shared" si="9"/>
         <v>2137.07467636802</v>
       </c>
-      <c r="J39" s="7">
+      <c r="J39" s="44">
         <f ca="1" t="shared" si="9"/>
         <v>3244.35317868595</v>
       </c>
-      <c r="K39" s="7">
+      <c r="K39" s="44">
         <f ca="1" t="shared" si="9"/>
         <v>3476.71857779061</v>
       </c>
-      <c r="L39" s="7">
+      <c r="L39" s="44">
         <f ca="1" t="shared" si="9"/>
         <v>4806.84334797885</v>
       </c>
-      <c r="M39" s="7">
+      <c r="M39" s="44">
         <f ca="1" t="shared" si="9"/>
         <v>4586.91595317548</v>
       </c>
-      <c r="N39" s="44">
+      <c r="N39" s="45">
         <f ca="1" t="shared" si="9"/>
         <v>6913.61829652249</v>
       </c>
@@ -3030,7 +3018,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:N2">
-    <cfRule type="colorScale" priority="24">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3042,7 +3030,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:N3">
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3054,7 +3042,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:N4">
-    <cfRule type="colorScale" priority="23">
+    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3066,7 +3054,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:N5">
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3078,7 +3066,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:N6">
-    <cfRule type="colorScale" priority="22">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3090,7 +3078,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:N7">
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3102,7 +3090,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:N8">
-    <cfRule type="colorScale" priority="21">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3114,7 +3102,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:N9">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3126,7 +3114,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:N10">
-    <cfRule type="colorScale" priority="20">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3138,7 +3126,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:N11">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3150,7 +3138,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12:N12">
-    <cfRule type="colorScale" priority="19">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3162,7 +3150,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:N13">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3174,7 +3162,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I14:N14">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3186,7 +3174,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15:N15">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3198,7 +3186,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16:N16">
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3210,7 +3198,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17:N17">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3222,7 +3210,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18:N18">
-    <cfRule type="colorScale" priority="16">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3234,7 +3222,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19:N19">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3246,7 +3234,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L20:N20">
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3258,7 +3246,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L21:N21">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3270,7 +3258,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M22:N22">
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3282,7 +3270,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3294,7 +3282,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3306,7 +3294,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3318,7 +3306,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C27:N27">
-    <cfRule type="colorScale" priority="32">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3330,7 +3318,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:N28">
-    <cfRule type="colorScale" priority="31">
+    <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3342,7 +3330,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:N30">
-    <cfRule type="colorScale" priority="36">
+    <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3354,7 +3342,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D31:N31">
-    <cfRule type="colorScale" priority="35">
+    <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3365,8 +3353,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D32:N32">
-    <cfRule type="colorScale" priority="34">
+  <conditionalFormatting sqref="C32:N32">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3377,8 +3365,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C34:N34">
-    <cfRule type="colorScale" priority="37">
+  <conditionalFormatting sqref="D32:N32">
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3389,8 +3377,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D35:N35">
-    <cfRule type="colorScale" priority="38">
+  <conditionalFormatting sqref="C34:N34">
+    <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3401,8 +3389,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D35:N35">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C36">
-    <cfRule type="colorScale" priority="40">
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3413,8 +3413,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D36:N36">
-    <cfRule type="colorScale" priority="41">
+  <conditionalFormatting sqref="C36:N36">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3425,7 +3425,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C38:N38">
+  <conditionalFormatting sqref="D36:N36">
     <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
@@ -3437,8 +3437,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C39:N39">
-    <cfRule type="colorScale" priority="42">
+  <conditionalFormatting sqref="C38:N38">
+    <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3449,8 +3449,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D39:N39">
-    <cfRule type="colorScale" priority="25">
+  <conditionalFormatting sqref="C39:N39">
+    <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3461,8 +3461,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D39:N39">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C40:N40">
-    <cfRule type="colorScale" priority="26">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3474,7 +3486,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C31:C32 C35">
-    <cfRule type="colorScale" priority="33">
+    <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3490,7 +3502,7 @@
   <pageSetup paperSize="5" scale="86" orientation="landscape" horizontalDpi="600"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A33:N33 A37:N37 A13:N28 D12:N12 A12:B12 A2:N11 C1:N1" formulaRange="1"/>
+    <ignoredError sqref="C1:N1 A2:N11 A12:B12 D12:N12 A13:N28 A37:N37 A33:N33" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3514,37 +3526,37 @@
       <c r="B1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N1" s="13" t="s">
@@ -3552,10 +3564,10 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>44652</v>
       </c>
-      <c r="B2" s="6" cm="1">
+      <c r="B2" s="7" cm="1">
         <f ca="1" t="array" ref="B2:B13">TRANSPOSE('Monthly_Cohort_&amp;_Matrix'!C30:N30)</f>
         <v>11871</v>
       </c>
@@ -3609,10 +3621,10 @@
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>44682</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="7">
         <v>15998</v>
       </c>
       <c r="C3" s="19" cm="1">
@@ -3665,10 +3677,10 @@
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>44713</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>19147</v>
       </c>
       <c r="C4" s="19" cm="1">
@@ -3721,10 +3733,10 @@
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>44743</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>19360</v>
       </c>
       <c r="C5" s="19" cm="1">
@@ -3777,10 +3789,10 @@
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>44774</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>18585</v>
       </c>
       <c r="C6" s="19" cm="1">
@@ -3833,10 +3845,10 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>44805</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>13772</v>
       </c>
       <c r="C7" s="19" cm="1">
@@ -3889,10 +3901,10 @@
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>44835</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>10553</v>
       </c>
       <c r="C8" s="19" cm="1">
@@ -3945,10 +3957,10 @@
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>44866</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>12935</v>
       </c>
       <c r="C9" s="19" cm="1">
@@ -4001,10 +4013,10 @@
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>44896</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>10997</v>
       </c>
       <c r="C10" s="19" cm="1">
@@ -4057,10 +4069,10 @@
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>44927</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>11697</v>
       </c>
       <c r="C11" s="19" cm="1">
@@ -4113,10 +4125,10 @@
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="5">
+      <c r="A12" s="6">
         <v>44958</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>11724</v>
       </c>
       <c r="C12" s="19" cm="1">
@@ -4169,7 +4181,7 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="9">
+      <c r="A13" s="10">
         <v>44986</v>
       </c>
       <c r="B13" s="16">
@@ -4231,37 +4243,37 @@
       <c r="B16" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="12" t="s">
+      <c r="K16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L16" s="12" t="s">
+      <c r="L16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="M16" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N16" s="13" t="s">
@@ -4269,10 +4281,10 @@
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="5">
+      <c r="A17" s="6">
         <v>44652</v>
       </c>
-      <c r="B17" s="6" cm="1">
+      <c r="B17" s="7" cm="1">
         <f ca="1" t="array" ref="B17:B28">TRANSPOSE('Monthly_Cohort_&amp;_Matrix'!C34:N34)</f>
         <v>3470489.01252315</v>
       </c>
@@ -4326,10 +4338,10 @@
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="5">
+      <c r="A18" s="6">
         <v>44682</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="7">
         <v>5119928.17410458</v>
       </c>
       <c r="C18" s="19" cm="1">
@@ -4382,10 +4394,10 @@
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="5">
+      <c r="A19" s="6">
         <v>44713</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="7">
         <v>3815355.2505326</v>
       </c>
       <c r="C19" s="19" cm="1">
@@ -4438,10 +4450,10 @@
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="5">
+      <c r="A20" s="6">
         <v>44743</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="7">
         <v>4547888.81180353</v>
       </c>
       <c r="C20" s="19" cm="1">
@@ -4494,10 +4506,10 @@
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>44774</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="7">
         <v>2906573.54102523</v>
       </c>
       <c r="C21" s="19" cm="1">
@@ -4550,10 +4562,10 @@
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="5">
+      <c r="A22" s="6">
         <v>44805</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="7">
         <v>2178295.91129921</v>
       </c>
       <c r="C22" s="19" cm="1">
@@ -4606,10 +4618,10 @@
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="5">
+      <c r="A23" s="6">
         <v>44835</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="7">
         <v>2894310.36115145</v>
       </c>
       <c r="C23" s="19" cm="1">
@@ -4662,10 +4674,10 @@
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="5">
+      <c r="A24" s="6">
         <v>44866</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="7">
         <v>3252521.61156486</v>
       </c>
       <c r="C24" s="19" cm="1">
@@ -4718,10 +4730,10 @@
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="5">
+      <c r="A25" s="6">
         <v>44896</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="7">
         <v>2753173.18996686</v>
       </c>
       <c r="C25" s="19" cm="1">
@@ -4774,10 +4786,10 @@
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="5">
+      <c r="A26" s="6">
         <v>44927</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="7">
         <v>3024628.88019842</v>
       </c>
       <c r="C26" s="19" cm="1">
@@ -4830,10 +4842,10 @@
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="5">
+      <c r="A27" s="6">
         <v>44958</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="7">
         <v>3526821.3583757</v>
       </c>
       <c r="C27" s="19" cm="1">
@@ -4886,7 +4898,7 @@
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="9">
+      <c r="A28" s="10">
         <v>44986</v>
       </c>
       <c r="B28" s="16">
@@ -4951,7 +4963,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{00ee62df-ee91-430c-9394-d9a2a2eda943}</x14:id>
+          <x14:id>{14b17256-cfe4-4cfd-b21e-2cc3d663d086}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4965,7 +4977,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6b0e1aa1-5f26-410d-8f58-c410f920d25a}</x14:id>
+          <x14:id>{bcb72351-2da1-477b-bca9-603760936b09}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4979,7 +4991,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7377222f-e273-4c1c-b120-d6b1d7b5900c}</x14:id>
+          <x14:id>{9c7a52ff-e9fb-46cb-86ed-a0a9f06cb5fb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4993,7 +5005,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8c79ce37-d316-423b-8343-a6c74c738110}</x14:id>
+          <x14:id>{22d7740f-938a-496c-be35-d6460c692b3b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5007,7 +5019,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5cd7b9f0-aff6-4b00-849d-3ee596d2b0d9}</x14:id>
+          <x14:id>{5f578f78-9d23-4e71-8b26-7a522d7ee613}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5021,7 +5033,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8518fbae-dd65-498f-b980-e4a4f2b40c3b}</x14:id>
+          <x14:id>{1d3bec2e-3ee5-4380-bec8-6638a8f79d10}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5035,7 +5047,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a3d3aab-a0c5-43e8-9b0b-908f1e5af53e}</x14:id>
+          <x14:id>{759521f0-91d5-49e3-a010-8cbe1fadb143}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5049,7 +5061,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41928ab7-fade-43d8-8369-cc84145f415f}</x14:id>
+          <x14:id>{db4a1ce7-374b-41f1-b7da-9249aa742b78}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5063,7 +5075,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{196fa351-f843-4722-880f-5e85f0964462}</x14:id>
+          <x14:id>{e84b094a-6f69-4be5-bc42-ec9d79c2311d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5077,7 +5089,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{18e3e541-cfad-44a6-8204-cef0506d3844}</x14:id>
+          <x14:id>{78c5ee94-07db-4f79-b2b7-6b2aa95a0733}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5091,7 +5103,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f1321b15-3d3a-4b08-b020-0eca664537ca}</x14:id>
+          <x14:id>{fc2b0092-4594-4321-a58a-341fd45f2488}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5105,7 +5117,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aa8382e4-4bb2-425c-b15d-6bffc31a0aae}</x14:id>
+          <x14:id>{8e79bfa1-685a-4fcb-879a-dcaaf13efd28}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5119,7 +5131,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c72994ea-fc78-4e30-80c1-4501e4e93586}</x14:id>
+          <x14:id>{61b1effd-172f-4025-91dc-3357ff350345}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5133,7 +5145,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{444b67de-b7a8-466e-a218-13648fa6d039}</x14:id>
+          <x14:id>{029fcab1-8edb-4089-968c-5f63484b70de}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5147,7 +5159,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3572ca7c-b2c4-4bcc-9e3f-badefb25cf2f}</x14:id>
+          <x14:id>{f2fb9e6b-148a-4edc-8459-6be9fbf805d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5161,7 +5173,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{644044ef-bd72-48d9-a6ce-a6e15a17bcce}</x14:id>
+          <x14:id>{51fdc7c2-ba75-4ae0-9d33-c21cb5e5a9c7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5175,7 +5187,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0ed80ad5-3ae8-4f89-8f6f-32553bd9bf5b}</x14:id>
+          <x14:id>{d323152b-9a0d-4989-a7bf-8552691c7e77}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5189,7 +5201,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0d0ba628-7b9b-4c1a-8e07-85a82c63e49c}</x14:id>
+          <x14:id>{3a1cdb21-51cb-44ba-a44e-0a223345dfa2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5203,7 +5215,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{041c0b72-6898-4a95-a925-25a47b1ed85c}</x14:id>
+          <x14:id>{cb5a4a42-47f5-4a37-bd9d-6c1a56f4c1f8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5217,7 +5229,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eb5319c4-199f-45d3-9736-7ded9d0f241c}</x14:id>
+          <x14:id>{2de166a1-e873-4161-84d4-8d4ca9c387c2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5231,7 +5243,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{34444ac5-13d5-4d96-97fc-575e325e81ba}</x14:id>
+          <x14:id>{f9c26b2b-1082-41ea-8656-7677c605cde0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5245,7 +5257,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5b20267f-b5e9-46a2-9a1a-905f0ed5d8bf}</x14:id>
+          <x14:id>{598b342a-e9d6-48a2-a5c3-a583fecaf12b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5259,7 +5271,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d7a07207-e9ed-4226-ad98-5bc43484a24f}</x14:id>
+          <x14:id>{acbb27b9-8d81-4fd3-9490-fd6e4640b919}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5273,7 +5285,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d7ffac16-0b1a-42c4-895c-0dc821fa1f9e}</x14:id>
+          <x14:id>{d5dd954a-62b4-4262-bc32-624c4647f098}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5286,7 +5298,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{00ee62df-ee91-430c-9394-d9a2a2eda943}">
+          <x14:cfRule type="dataBar" id="{14b17256-cfe4-4cfd-b21e-2cc3d663d086}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5299,7 +5311,7 @@
           <xm:sqref>C2:C13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6b0e1aa1-5f26-410d-8f58-c410f920d25a}">
+          <x14:cfRule type="dataBar" id="{bcb72351-2da1-477b-bca9-603760936b09}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5312,7 +5324,7 @@
           <xm:sqref>C17:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7377222f-e273-4c1c-b120-d6b1d7b5900c}">
+          <x14:cfRule type="dataBar" id="{9c7a52ff-e9fb-46cb-86ed-a0a9f06cb5fb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5325,7 +5337,7 @@
           <xm:sqref>D2:D13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8c79ce37-d316-423b-8343-a6c74c738110}">
+          <x14:cfRule type="dataBar" id="{22d7740f-938a-496c-be35-d6460c692b3b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5338,7 +5350,7 @@
           <xm:sqref>D17:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5cd7b9f0-aff6-4b00-849d-3ee596d2b0d9}">
+          <x14:cfRule type="dataBar" id="{5f578f78-9d23-4e71-8b26-7a522d7ee613}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5351,7 +5363,7 @@
           <xm:sqref>E2:E13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8518fbae-dd65-498f-b980-e4a4f2b40c3b}">
+          <x14:cfRule type="dataBar" id="{1d3bec2e-3ee5-4380-bec8-6638a8f79d10}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5364,7 +5376,7 @@
           <xm:sqref>E17:E28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4a3d3aab-a0c5-43e8-9b0b-908f1e5af53e}">
+          <x14:cfRule type="dataBar" id="{759521f0-91d5-49e3-a010-8cbe1fadb143}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5377,7 +5389,7 @@
           <xm:sqref>F2:F13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{41928ab7-fade-43d8-8369-cc84145f415f}">
+          <x14:cfRule type="dataBar" id="{db4a1ce7-374b-41f1-b7da-9249aa742b78}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5390,7 +5402,7 @@
           <xm:sqref>F17:F28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{196fa351-f843-4722-880f-5e85f0964462}">
+          <x14:cfRule type="dataBar" id="{e84b094a-6f69-4be5-bc42-ec9d79c2311d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5403,7 +5415,7 @@
           <xm:sqref>G2:G13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{18e3e541-cfad-44a6-8204-cef0506d3844}">
+          <x14:cfRule type="dataBar" id="{78c5ee94-07db-4f79-b2b7-6b2aa95a0733}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5416,7 +5428,7 @@
           <xm:sqref>G17:G28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f1321b15-3d3a-4b08-b020-0eca664537ca}">
+          <x14:cfRule type="dataBar" id="{fc2b0092-4594-4321-a58a-341fd45f2488}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5429,7 +5441,7 @@
           <xm:sqref>H2:H13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aa8382e4-4bb2-425c-b15d-6bffc31a0aae}">
+          <x14:cfRule type="dataBar" id="{8e79bfa1-685a-4fcb-879a-dcaaf13efd28}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5442,7 +5454,7 @@
           <xm:sqref>H17:H28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c72994ea-fc78-4e30-80c1-4501e4e93586}">
+          <x14:cfRule type="dataBar" id="{61b1effd-172f-4025-91dc-3357ff350345}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5455,7 +5467,7 @@
           <xm:sqref>I2:I13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{444b67de-b7a8-466e-a218-13648fa6d039}">
+          <x14:cfRule type="dataBar" id="{029fcab1-8edb-4089-968c-5f63484b70de}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5468,7 +5480,7 @@
           <xm:sqref>I17:I28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3572ca7c-b2c4-4bcc-9e3f-badefb25cf2f}">
+          <x14:cfRule type="dataBar" id="{f2fb9e6b-148a-4edc-8459-6be9fbf805d5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5481,7 +5493,7 @@
           <xm:sqref>J2:J13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{644044ef-bd72-48d9-a6ce-a6e15a17bcce}">
+          <x14:cfRule type="dataBar" id="{51fdc7c2-ba75-4ae0-9d33-c21cb5e5a9c7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5494,7 +5506,7 @@
           <xm:sqref>J17:J28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0ed80ad5-3ae8-4f89-8f6f-32553bd9bf5b}">
+          <x14:cfRule type="dataBar" id="{d323152b-9a0d-4989-a7bf-8552691c7e77}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5507,7 +5519,7 @@
           <xm:sqref>K2:K13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0d0ba628-7b9b-4c1a-8e07-85a82c63e49c}">
+          <x14:cfRule type="dataBar" id="{3a1cdb21-51cb-44ba-a44e-0a223345dfa2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5520,7 +5532,7 @@
           <xm:sqref>K17:K28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{041c0b72-6898-4a95-a925-25a47b1ed85c}">
+          <x14:cfRule type="dataBar" id="{cb5a4a42-47f5-4a37-bd9d-6c1a56f4c1f8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5533,7 +5545,7 @@
           <xm:sqref>L2:L13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eb5319c4-199f-45d3-9736-7ded9d0f241c}">
+          <x14:cfRule type="dataBar" id="{2de166a1-e873-4161-84d4-8d4ca9c387c2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5546,7 +5558,7 @@
           <xm:sqref>L17:L28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{34444ac5-13d5-4d96-97fc-575e325e81ba}">
+          <x14:cfRule type="dataBar" id="{f9c26b2b-1082-41ea-8656-7677c605cde0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5559,7 +5571,7 @@
           <xm:sqref>M2:M13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5b20267f-b5e9-46a2-9a1a-905f0ed5d8bf}">
+          <x14:cfRule type="dataBar" id="{598b342a-e9d6-48a2-a5c3-a583fecaf12b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5572,7 +5584,7 @@
           <xm:sqref>M17:M28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d7a07207-e9ed-4226-ad98-5bc43484a24f}">
+          <x14:cfRule type="dataBar" id="{acbb27b9-8d81-4fd3-9490-fd6e4640b919}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5585,7 +5597,7 @@
           <xm:sqref>N2:N13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d7ffac16-0b1a-42c4-895c-0dc821fa1f9e}">
+          <x14:cfRule type="dataBar" id="{d5dd954a-62b4-4262-bc32-624c4647f098}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -5622,37 +5634,37 @@
       <c r="B1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N1" s="13" t="s">
@@ -5660,10 +5672,10 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>44652</v>
       </c>
-      <c r="B2" s="6" cm="1">
+      <c r="B2" s="7" cm="1">
         <f ca="1" t="array" ref="B2:B13">TRANSPOSE('Monthly_Cohort_&amp;_Matrix'!C30:N30)</f>
         <v>11871</v>
       </c>
@@ -5717,10 +5729,10 @@
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>44682</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="7">
         <v>15998</v>
       </c>
       <c r="C3" s="14" cm="1">
@@ -5773,10 +5785,10 @@
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>44713</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>19147</v>
       </c>
       <c r="C4" s="14" cm="1">
@@ -5829,10 +5841,10 @@
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>44743</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>19360</v>
       </c>
       <c r="C5" s="14" cm="1">
@@ -5885,10 +5897,10 @@
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>44774</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>18585</v>
       </c>
       <c r="C6" s="14" cm="1">
@@ -5941,10 +5953,10 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>44805</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>13772</v>
       </c>
       <c r="C7" s="14" cm="1">
@@ -5997,10 +6009,10 @@
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>44835</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>10553</v>
       </c>
       <c r="C8" s="14" cm="1">
@@ -6053,10 +6065,10 @@
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>44866</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>12935</v>
       </c>
       <c r="C9" s="14" cm="1">
@@ -6109,10 +6121,10 @@
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>44896</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>10997</v>
       </c>
       <c r="C10" s="14" cm="1">
@@ -6165,10 +6177,10 @@
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>44927</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>11697</v>
       </c>
       <c r="C11" s="14" cm="1">
@@ -6221,10 +6233,10 @@
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="5">
+      <c r="A12" s="6">
         <v>44958</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>11724</v>
       </c>
       <c r="C12" s="14" cm="1">
@@ -6277,7 +6289,7 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="9">
+      <c r="A13" s="10">
         <v>44986</v>
       </c>
       <c r="B13" s="16">
@@ -6339,37 +6351,37 @@
       <c r="B16" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="12" t="s">
+      <c r="K16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L16" s="12" t="s">
+      <c r="L16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="M16" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N16" s="13" t="s">
@@ -6377,10 +6389,10 @@
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="5">
+      <c r="A17" s="6">
         <v>44652</v>
       </c>
-      <c r="B17" s="6" cm="1">
+      <c r="B17" s="7" cm="1">
         <f ca="1" t="array" ref="B17:B28">TRANSPOSE('Monthly_Cohort_&amp;_Matrix'!C34:N34)</f>
         <v>3470489.01252315</v>
       </c>
@@ -6434,10 +6446,10 @@
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="5">
+      <c r="A18" s="6">
         <v>44682</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="7">
         <v>5119928.17410458</v>
       </c>
       <c r="C18" s="14" cm="1">
@@ -6490,10 +6502,10 @@
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="5">
+      <c r="A19" s="6">
         <v>44713</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="7">
         <v>3815355.2505326</v>
       </c>
       <c r="C19" s="14" cm="1">
@@ -6546,10 +6558,10 @@
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="5">
+      <c r="A20" s="6">
         <v>44743</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="7">
         <v>4547888.81180353</v>
       </c>
       <c r="C20" s="14" cm="1">
@@ -6602,10 +6614,10 @@
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>44774</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="7">
         <v>2906573.54102523</v>
       </c>
       <c r="C21" s="14" cm="1">
@@ -6658,10 +6670,10 @@
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="5">
+      <c r="A22" s="6">
         <v>44805</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="7">
         <v>2178295.91129921</v>
       </c>
       <c r="C22" s="14" cm="1">
@@ -6714,10 +6726,10 @@
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="5">
+      <c r="A23" s="6">
         <v>44835</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="7">
         <v>2894310.36115145</v>
       </c>
       <c r="C23" s="14" cm="1">
@@ -6770,10 +6782,10 @@
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="5">
+      <c r="A24" s="6">
         <v>44866</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="7">
         <v>3252521.61156486</v>
       </c>
       <c r="C24" s="14" cm="1">
@@ -6826,10 +6838,10 @@
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="5">
+      <c r="A25" s="6">
         <v>44896</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="7">
         <v>2753173.18996686</v>
       </c>
       <c r="C25" s="14" cm="1">
@@ -6882,10 +6894,10 @@
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="5">
+      <c r="A26" s="6">
         <v>44927</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="7">
         <v>3024628.88019842</v>
       </c>
       <c r="C26" s="14" cm="1">
@@ -6938,10 +6950,10 @@
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="5">
+      <c r="A27" s="6">
         <v>44958</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="7">
         <v>3526821.3583757</v>
       </c>
       <c r="C27" s="14" cm="1">
@@ -6994,7 +7006,7 @@
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="9">
+      <c r="A28" s="10">
         <v>44986</v>
       </c>
       <c r="B28" s="16">
@@ -7059,7 +7071,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1c0501a5-134a-4284-b9f8-3496f0da0246}</x14:id>
+          <x14:id>{1b6d4a38-1986-4e42-a11b-9e97693b1d88}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7073,7 +7085,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b1b439e2-4329-41ae-9795-19c6f43e2eaf}</x14:id>
+          <x14:id>{9299799e-45ed-4f62-9c1f-d88a7ae4df79}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7087,7 +7099,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{44970ec6-46d9-4d44-9670-0a96ab2d943a}</x14:id>
+          <x14:id>{fb4c9798-d005-4d17-9551-d85205d56229}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7101,7 +7113,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f9405f8f-78c9-4370-82fd-b0d4a85b2ce6}</x14:id>
+          <x14:id>{71fcf1d2-cc81-43fe-aaa3-e57cface15b1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7115,7 +7127,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{90a92d30-b84d-47a8-b9c4-e1a8879a198e}</x14:id>
+          <x14:id>{07d2af5b-41cd-4587-a634-590d29deb743}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7129,7 +7141,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b2858975-0a84-41ef-b206-a748e8bcab6b}</x14:id>
+          <x14:id>{fc178442-6959-4bf9-b502-be6eca2d2974}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7143,7 +7155,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0fc4c61c-bbd3-466e-b14a-664d5f6f42c9}</x14:id>
+          <x14:id>{b168352a-f7d5-4816-a71a-b7ce3abe2237}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7157,7 +7169,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e45e6a17-480c-491c-8c00-04d46214abd6}</x14:id>
+          <x14:id>{0087b8dc-8269-4f0e-9968-c703153493a2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7171,7 +7183,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{091b6d31-bc63-4e9e-bf01-0b58948c6697}</x14:id>
+          <x14:id>{a7c667d0-2528-4fa4-a056-c476689f4704}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7185,7 +7197,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a24c7272-e532-478d-8e39-a31f5e5c2aff}</x14:id>
+          <x14:id>{ecb9b942-f358-4077-b616-8d089b5f221e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7199,7 +7211,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{378b78a9-2af3-4c1d-a1d1-745ff7ca0404}</x14:id>
+          <x14:id>{118f442e-6712-4975-a6b8-974b94e403c8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7213,7 +7225,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62a31d65-ccdd-40a1-b886-0569aa29f6c1}</x14:id>
+          <x14:id>{c37d9cb1-6c88-4587-a7b9-a34df116bc7d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7227,7 +7239,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24c19153-6e98-4286-ba83-3a6a5afff786}</x14:id>
+          <x14:id>{311c1848-5c58-44f2-ac5c-257d2ee7225d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7241,7 +7253,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{43949d9b-0372-479d-b2b2-3c436fdfbd18}</x14:id>
+          <x14:id>{7f6b95df-f6d4-48fb-b0cf-445c9c7c8572}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7255,7 +7267,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9a07728b-ba06-4f9b-96fb-cd2e73f62f26}</x14:id>
+          <x14:id>{4538d740-7d36-4cf6-820a-20351886b934}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7269,7 +7281,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e7c79a53-ae83-475a-bbed-e72a6dff762b}</x14:id>
+          <x14:id>{580bc3cb-8a50-4fa3-bd22-aa4e09457eae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7283,7 +7295,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{593bf600-9fa2-44d9-b677-b1d854089210}</x14:id>
+          <x14:id>{19bc5f7e-60bd-4c07-8430-b50fa7a6a26f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7297,7 +7309,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d3bd9ac6-aa87-4d9a-a05f-cf0182fc2b57}</x14:id>
+          <x14:id>{d186fd79-315b-4830-ad04-a7b013a3a353}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7311,7 +7323,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e10157cf-9d4a-4030-a7f7-f1f87e63cce5}</x14:id>
+          <x14:id>{71473b36-7582-4e5d-b5c1-cad86b4cacbb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7325,7 +7337,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cfc340ba-667a-42b2-9afc-d743eed2841c}</x14:id>
+          <x14:id>{a6ed8167-99fb-45a5-88fe-e13b291b7ed4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7339,7 +7351,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5be02806-3c34-419a-ac3d-fd509c8b51a7}</x14:id>
+          <x14:id>{d26f413a-e112-4006-9454-d42ee9dc80a4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7353,7 +7365,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{104c1857-22fe-4ca9-b4c6-b1d501c250f6}</x14:id>
+          <x14:id>{6e33de3b-3de8-4e6e-991b-2a13dc5fd558}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7367,7 +7379,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e319005a-11cf-4de5-a066-6220cfcd6035}</x14:id>
+          <x14:id>{ed8ce0af-b3d8-49fc-92c1-b8e657615151}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7381,7 +7393,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a6252077-b112-466d-8605-5f1861abfeba}</x14:id>
+          <x14:id>{c8968156-e10d-46f1-b9e1-4979b8954de8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7394,7 +7406,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1c0501a5-134a-4284-b9f8-3496f0da0246}">
+          <x14:cfRule type="dataBar" id="{1b6d4a38-1986-4e42-a11b-9e97693b1d88}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7407,7 +7419,7 @@
           <xm:sqref>C2:C13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b1b439e2-4329-41ae-9795-19c6f43e2eaf}">
+          <x14:cfRule type="dataBar" id="{9299799e-45ed-4f62-9c1f-d88a7ae4df79}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7420,7 +7432,7 @@
           <xm:sqref>C17:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{44970ec6-46d9-4d44-9670-0a96ab2d943a}">
+          <x14:cfRule type="dataBar" id="{fb4c9798-d005-4d17-9551-d85205d56229}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7433,7 +7445,7 @@
           <xm:sqref>D2:D13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f9405f8f-78c9-4370-82fd-b0d4a85b2ce6}">
+          <x14:cfRule type="dataBar" id="{71fcf1d2-cc81-43fe-aaa3-e57cface15b1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7446,7 +7458,7 @@
           <xm:sqref>D17:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{90a92d30-b84d-47a8-b9c4-e1a8879a198e}">
+          <x14:cfRule type="dataBar" id="{07d2af5b-41cd-4587-a634-590d29deb743}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7459,7 +7471,7 @@
           <xm:sqref>E2:E13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b2858975-0a84-41ef-b206-a748e8bcab6b}">
+          <x14:cfRule type="dataBar" id="{fc178442-6959-4bf9-b502-be6eca2d2974}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7472,7 +7484,7 @@
           <xm:sqref>E17:E28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0fc4c61c-bbd3-466e-b14a-664d5f6f42c9}">
+          <x14:cfRule type="dataBar" id="{b168352a-f7d5-4816-a71a-b7ce3abe2237}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7485,7 +7497,7 @@
           <xm:sqref>F2:F13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e45e6a17-480c-491c-8c00-04d46214abd6}">
+          <x14:cfRule type="dataBar" id="{0087b8dc-8269-4f0e-9968-c703153493a2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7498,7 +7510,7 @@
           <xm:sqref>F17:F28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{091b6d31-bc63-4e9e-bf01-0b58948c6697}">
+          <x14:cfRule type="dataBar" id="{a7c667d0-2528-4fa4-a056-c476689f4704}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7511,7 +7523,7 @@
           <xm:sqref>G2:G13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a24c7272-e532-478d-8e39-a31f5e5c2aff}">
+          <x14:cfRule type="dataBar" id="{ecb9b942-f358-4077-b616-8d089b5f221e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7524,7 +7536,7 @@
           <xm:sqref>G17:G28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{378b78a9-2af3-4c1d-a1d1-745ff7ca0404}">
+          <x14:cfRule type="dataBar" id="{118f442e-6712-4975-a6b8-974b94e403c8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7537,7 +7549,7 @@
           <xm:sqref>H2:H13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{62a31d65-ccdd-40a1-b886-0569aa29f6c1}">
+          <x14:cfRule type="dataBar" id="{c37d9cb1-6c88-4587-a7b9-a34df116bc7d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7550,7 +7562,7 @@
           <xm:sqref>H17:H28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{24c19153-6e98-4286-ba83-3a6a5afff786}">
+          <x14:cfRule type="dataBar" id="{311c1848-5c58-44f2-ac5c-257d2ee7225d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7563,7 +7575,7 @@
           <xm:sqref>I2:I13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{43949d9b-0372-479d-b2b2-3c436fdfbd18}">
+          <x14:cfRule type="dataBar" id="{7f6b95df-f6d4-48fb-b0cf-445c9c7c8572}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7576,7 +7588,7 @@
           <xm:sqref>I17:I28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9a07728b-ba06-4f9b-96fb-cd2e73f62f26}">
+          <x14:cfRule type="dataBar" id="{4538d740-7d36-4cf6-820a-20351886b934}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7589,7 +7601,7 @@
           <xm:sqref>J2:J13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e7c79a53-ae83-475a-bbed-e72a6dff762b}">
+          <x14:cfRule type="dataBar" id="{580bc3cb-8a50-4fa3-bd22-aa4e09457eae}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7602,7 +7614,7 @@
           <xm:sqref>J17:J28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{593bf600-9fa2-44d9-b677-b1d854089210}">
+          <x14:cfRule type="dataBar" id="{19bc5f7e-60bd-4c07-8430-b50fa7a6a26f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7615,7 +7627,7 @@
           <xm:sqref>K2:K13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d3bd9ac6-aa87-4d9a-a05f-cf0182fc2b57}">
+          <x14:cfRule type="dataBar" id="{d186fd79-315b-4830-ad04-a7b013a3a353}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7628,7 +7640,7 @@
           <xm:sqref>K17:K28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e10157cf-9d4a-4030-a7f7-f1f87e63cce5}">
+          <x14:cfRule type="dataBar" id="{71473b36-7582-4e5d-b5c1-cad86b4cacbb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7641,7 +7653,7 @@
           <xm:sqref>L2:L13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cfc340ba-667a-42b2-9afc-d743eed2841c}">
+          <x14:cfRule type="dataBar" id="{a6ed8167-99fb-45a5-88fe-e13b291b7ed4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7654,7 +7666,7 @@
           <xm:sqref>L17:L28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5be02806-3c34-419a-ac3d-fd509c8b51a7}">
+          <x14:cfRule type="dataBar" id="{d26f413a-e112-4006-9454-d42ee9dc80a4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7667,7 +7679,7 @@
           <xm:sqref>M2:M13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{104c1857-22fe-4ca9-b4c6-b1d501c250f6}">
+          <x14:cfRule type="dataBar" id="{6e33de3b-3de8-4e6e-991b-2a13dc5fd558}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7680,7 +7692,7 @@
           <xm:sqref>M17:M28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e319005a-11cf-4de5-a066-6220cfcd6035}">
+          <x14:cfRule type="dataBar" id="{ed8ce0af-b3d8-49fc-92c1-b8e657615151}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7693,7 +7705,7 @@
           <xm:sqref>N2:N13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a6252077-b112-466d-8605-5f1861abfeba}">
+          <x14:cfRule type="dataBar" id="{c8968156-e10d-46f1-b9e1-4979b8954de8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7720,13 +7732,16 @@
   <sheetFormatPr defaultColWidth="8.79279279279279" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.4774774774775" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1801801801802" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7657657657658" style="1" customWidth="1"/>
-    <col min="4" max="7" width="13.7657657657658" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.3783783783784" style="1" customWidth="1"/>
+    <col min="3" max="5" width="13.7657657657658" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.3603603603604" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.4594594594595" style="2" customWidth="1"/>
     <col min="8" max="8" width="2.48648648648649" style="2" customWidth="1"/>
     <col min="9" max="9" width="11.4774774774775" style="2" customWidth="1"/>
-    <col min="10" max="10" width="11.1801801801802" style="2" customWidth="1"/>
-    <col min="11" max="15" width="13.954954954955" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.3783783783784" style="2" customWidth="1"/>
+    <col min="11" max="13" width="13.954954954955" style="2" customWidth="1"/>
+    <col min="14" max="14" width="14.3603603603604" style="2" customWidth="1"/>
+    <col min="15" max="15" width="15.4594594594595" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -7736,19 +7751,19 @@
       <c r="B1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>32</v>
       </c>
       <c r="I1" s="3" t="s">
@@ -7757,1293 +7772,1293 @@
       <c r="J1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>44652</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="7">
         <f t="shared" ref="B2:B13" si="0">SUM(C2:G2)</f>
         <v>11871</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="8">
         <v>11871</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="8">
         <v>0</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <v>0</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="8">
         <v>0</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="8">
         <v>0</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="6">
         <v>44652</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="7">
         <f t="shared" ref="J2:J13" si="1">B2</f>
         <v>11871</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="9">
         <f t="shared" ref="K2:O2" si="2">IFERROR(C2/$B2,0)</f>
         <v>1</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>44682</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="7">
         <f t="shared" si="0"/>
         <v>17402</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="8">
         <v>15998</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="8">
         <v>1404</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="8">
         <v>0</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="8">
         <v>0</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="8">
         <v>0</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="6">
         <v>44682</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="7">
         <f t="shared" si="1"/>
         <v>17402</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="9">
         <f t="shared" ref="K3:O3" si="3">IFERROR(C3/$B3,0)</f>
         <v>0.919319618434663</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="9">
         <f t="shared" si="3"/>
         <v>0.0806803815653373</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M3" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N3" s="8">
+      <c r="N3" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O3" s="8">
+      <c r="O3" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>44713</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <f t="shared" si="0"/>
         <v>21714</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="8">
         <v>19147</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="8">
         <v>1924</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="8">
         <v>643</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="8">
         <v>0</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="8">
         <v>0</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="6">
         <v>44713</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="7">
         <f t="shared" si="1"/>
         <v>21714</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="9">
         <f t="shared" ref="K4:O4" si="4">IFERROR(C4/$B4,0)</f>
         <v>0.881781339228148</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="9">
         <f t="shared" si="4"/>
         <v>0.0886064290319609</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="9">
         <f t="shared" si="4"/>
         <v>0.0296122317398913</v>
       </c>
-      <c r="N4" s="8">
+      <c r="N4" s="9">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O4" s="8">
+      <c r="O4" s="9">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>44743</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <f t="shared" si="0"/>
         <v>22982</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="8">
         <v>19360</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="8">
         <v>2181</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <v>916</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="8">
         <v>525</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="8">
         <v>0</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="6">
         <v>44743</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="7">
         <f t="shared" si="1"/>
         <v>22982</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="9">
         <f t="shared" ref="K5:O5" si="5">IFERROR(C5/$B5,0)</f>
         <v>0.842398398746845</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="9">
         <f t="shared" si="5"/>
         <v>0.0949003568009747</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="9">
         <f t="shared" si="5"/>
         <v>0.0398572796101297</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N5" s="9">
         <f t="shared" si="5"/>
         <v>0.0228439648420503</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="9">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>44774</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f t="shared" si="0"/>
         <v>21920</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <v>18585</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <v>1688</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <v>693</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <v>954</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <v>0</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="6">
         <v>44774</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="7">
         <f t="shared" si="1"/>
         <v>21920</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="9">
         <f t="shared" ref="K6:O6" si="6">IFERROR(C6/$B6,0)</f>
         <v>0.847855839416058</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="9">
         <f t="shared" si="6"/>
         <v>0.077007299270073</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="9">
         <f t="shared" si="6"/>
         <v>0.0316149635036496</v>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="9">
         <f t="shared" si="6"/>
         <v>0.043521897810219</v>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="9">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>44805</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <f t="shared" si="0"/>
         <v>17502</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <v>13772</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <v>1496</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <v>831</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <v>1403</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="8">
         <v>0</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="6">
         <v>44805</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="7">
         <f t="shared" si="1"/>
         <v>17502</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="9">
         <f t="shared" ref="K7:O7" si="7">IFERROR(C7/$B7,0)</f>
         <v>0.786881499257228</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="9">
         <f t="shared" si="7"/>
         <v>0.0854759456062164</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M7" s="9">
         <f t="shared" si="7"/>
         <v>0.0474802879670895</v>
       </c>
-      <c r="N7" s="8">
+      <c r="N7" s="9">
         <f t="shared" si="7"/>
         <v>0.0801622671694664</v>
       </c>
-      <c r="O7" s="8">
+      <c r="O7" s="9">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>44835</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <f t="shared" si="0"/>
         <v>14319</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>10553</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <v>1098</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <v>726</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>1614</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <v>328</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="6">
         <v>44835</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="7">
         <f t="shared" si="1"/>
         <v>14319</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="9">
         <f t="shared" ref="K8:O8" si="8">IFERROR(C8/$B8,0)</f>
         <v>0.736992806760249</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="9">
         <f t="shared" si="8"/>
         <v>0.076681332495286</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="9">
         <f t="shared" si="8"/>
         <v>0.050701864655353</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="9">
         <f t="shared" si="8"/>
         <v>0.112717368531322</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="9">
         <f t="shared" si="8"/>
         <v>0.0229066275577903</v>
       </c>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>44866</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <f t="shared" si="0"/>
         <v>16063</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <v>12935</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <v>952</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <v>451</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <v>1125</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <v>600</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="6">
         <v>44866</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="7">
         <f t="shared" si="1"/>
         <v>16063</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="9">
         <f t="shared" ref="K9:O9" si="9">IFERROR(C9/$B9,0)</f>
         <v>0.805266762124136</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="9">
         <f t="shared" si="9"/>
         <v>0.0592666376143933</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="9">
         <f t="shared" si="9"/>
         <v>0.0280769470211044</v>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="9">
         <f t="shared" si="9"/>
         <v>0.0700367303741518</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="9">
         <f t="shared" si="9"/>
         <v>0.0373529228662143</v>
       </c>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>44896</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <f t="shared" si="0"/>
         <v>14594</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>10997</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <v>1222</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <v>449</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <v>1059</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="8">
         <v>867</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="6">
         <v>44896</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="7">
         <f t="shared" si="1"/>
         <v>14594</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="9">
         <f t="shared" ref="K10:O10" si="10">IFERROR(C10/$B10,0)</f>
         <v>0.753528847471564</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="9">
         <f t="shared" si="10"/>
         <v>0.0837330409757435</v>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="9">
         <f t="shared" si="10"/>
         <v>0.0307660682472249</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="9">
         <f t="shared" si="10"/>
         <v>0.0725640674249692</v>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="9">
         <f t="shared" si="10"/>
         <v>0.0594079758804988</v>
       </c>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>44927</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <f t="shared" si="0"/>
         <v>14870</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <v>11697</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <v>860</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <v>415</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <v>786</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="8">
         <v>1112</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="6">
         <v>44927</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="7">
         <f t="shared" si="1"/>
         <v>14870</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="9">
         <f t="shared" ref="K11:O11" si="11">IFERROR(C11/$B11,0)</f>
         <v>0.786617350369872</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="9">
         <f t="shared" si="11"/>
         <v>0.0578345662407532</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="9">
         <f t="shared" si="11"/>
         <v>0.0279085406859449</v>
       </c>
-      <c r="N11" s="8">
+      <c r="N11" s="9">
         <f t="shared" si="11"/>
         <v>0.0528581035642233</v>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="9">
         <f t="shared" si="11"/>
         <v>0.0747814391392065</v>
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="5">
+      <c r="A12" s="6">
         <v>44958</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <f t="shared" si="0"/>
         <v>15032</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <v>11724</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <v>996</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <v>373</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="8">
         <v>669</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="8">
         <v>1270</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="6">
         <v>44958</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="7">
         <f t="shared" si="1"/>
         <v>15032</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="9">
         <f t="shared" ref="K12:O12" si="12">IFERROR(C12/$B12,0)</f>
         <v>0.779936136242682</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="9">
         <f t="shared" si="12"/>
         <v>0.0662586482171368</v>
       </c>
-      <c r="M12" s="8">
+      <c r="M12" s="9">
         <f t="shared" si="12"/>
         <v>0.0248137307078233</v>
       </c>
-      <c r="N12" s="8">
+      <c r="N12" s="9">
         <f t="shared" si="12"/>
         <v>0.0445050558807877</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="9">
         <f t="shared" si="12"/>
         <v>0.08448642895157</v>
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="9">
+      <c r="A13" s="10">
         <v>44986</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <f t="shared" si="0"/>
         <v>17610</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="8">
         <v>14383</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="8">
         <v>855</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="8">
         <v>454</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="8">
         <v>649</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="8">
         <v>1269</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="10">
         <v>44986</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="7">
         <f t="shared" si="1"/>
         <v>17610</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="9">
         <f t="shared" ref="K13:O13" si="13">IFERROR(C13/$B13,0)</f>
         <v>0.816751845542306</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="9">
         <f t="shared" si="13"/>
         <v>0.0485519591141397</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="9">
         <f t="shared" si="13"/>
         <v>0.0257808063600227</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N13" s="9">
         <f t="shared" si="13"/>
         <v>0.0368540601930721</v>
       </c>
-      <c r="O13" s="8">
+      <c r="O13" s="9">
         <f t="shared" si="13"/>
         <v>0.07206132879046</v>
       </c>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I15" s="10" t="s">
+      <c r="C15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="K15" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="N15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="O15" s="11" t="s">
-        <v>38</v>
+      <c r="K15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="5">
+      <c r="A16" s="6">
         <v>44652</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <f t="shared" ref="B16:B27" si="14">SUM(C16:G16)</f>
         <v>3470489.01252315</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <v>3470489.01252315</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="8">
         <v>0</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="8">
         <v>0</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="8">
         <v>0</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="8">
         <v>0</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="6">
         <v>44652</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="7">
         <f t="shared" ref="J16:J27" si="15">B16</f>
         <v>3470489.01252315</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="9">
         <f t="shared" ref="K16:O16" si="16">IFERROR(C16/$B16,0)</f>
         <v>1</v>
       </c>
-      <c r="L16" s="8">
+      <c r="L16" s="9">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M16" s="8">
+      <c r="M16" s="9">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="N16" s="8">
+      <c r="N16" s="9">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="O16" s="8">
+      <c r="O16" s="9">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="5">
+      <c r="A17" s="6">
         <v>44682</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <f t="shared" si="14"/>
         <v>9651773.84755788</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <v>5119928.17410458</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <v>4531845.6734533</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <v>0</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="8">
         <v>0</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="8">
         <v>0</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="6">
         <v>44682</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="7">
         <f t="shared" si="15"/>
         <v>9651773.84755788</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="9">
         <f t="shared" ref="K17:O17" si="17">IFERROR(C17/$B17,0)</f>
         <v>0.530464995861879</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L17" s="9">
         <f t="shared" si="17"/>
         <v>0.469535004138121</v>
       </c>
-      <c r="M17" s="8">
+      <c r="M17" s="9">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="N17" s="8">
+      <c r="N17" s="9">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="O17" s="8">
+      <c r="O17" s="9">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="5">
+      <c r="A18" s="6">
         <v>44713</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="7">
         <f t="shared" si="14"/>
         <v>9083109.40151623</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <v>3815355.2505326</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="8">
         <v>3251729.44022218</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="8">
         <v>2016024.71076145</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="8">
         <v>0</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="8">
         <v>0</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="6">
         <v>44713</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="7">
         <f t="shared" si="15"/>
         <v>9083109.40151623</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="9">
         <f t="shared" ref="K18:O18" si="18">IFERROR(C18/$B18,0)</f>
         <v>0.420049465648372</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="9">
         <f t="shared" si="18"/>
         <v>0.357997387951682</v>
       </c>
-      <c r="M18" s="8">
+      <c r="M18" s="9">
         <f t="shared" si="18"/>
         <v>0.221953146399945</v>
       </c>
-      <c r="N18" s="8">
+      <c r="N18" s="9">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O18" s="8">
+      <c r="O18" s="9">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="5">
+      <c r="A19" s="6">
         <v>44743</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="7">
         <f t="shared" si="14"/>
         <v>10710229.9726867</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>4547888.81180353</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <v>2577614.24978113</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="8">
         <v>2104764.61018048</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="8">
         <v>1479962.3009216</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="8">
         <v>0</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="6">
         <v>44743</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="7">
         <f t="shared" si="15"/>
         <v>10710229.9726867</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="9">
         <f t="shared" ref="K19:O19" si="19">IFERROR(C19/$B19,0)</f>
         <v>0.424630360263185</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="9">
         <f t="shared" si="19"/>
         <v>0.240668431616741</v>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="9">
         <f t="shared" si="19"/>
         <v>0.196519086476019</v>
       </c>
-      <c r="N19" s="8">
+      <c r="N19" s="9">
         <f t="shared" si="19"/>
         <v>0.138182121644055</v>
       </c>
-      <c r="O19" s="8">
+      <c r="O19" s="9">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="5">
+      <c r="A20" s="6">
         <v>44774</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="7">
         <f t="shared" si="14"/>
         <v>11849191.7532346</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>2906573.54102523</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="8">
         <v>4166630.58124646</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="8">
         <v>1433445.3502219</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="8">
         <v>3342542.28074097</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="8">
         <v>0</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="6">
         <v>44774</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="7">
         <f t="shared" si="15"/>
         <v>11849191.7532346</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20" s="9">
         <f t="shared" ref="K20:O20" si="20">IFERROR(C20/$B20,0)</f>
         <v>0.245297198455059</v>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="9">
         <f t="shared" si="20"/>
         <v>0.351638379057294</v>
       </c>
-      <c r="M20" s="8">
+      <c r="M20" s="9">
         <f t="shared" si="20"/>
         <v>0.120974103556945</v>
       </c>
-      <c r="N20" s="8">
+      <c r="N20" s="9">
         <f t="shared" si="20"/>
         <v>0.282090318930701</v>
       </c>
-      <c r="O20" s="8">
+      <c r="O20" s="9">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>44805</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="7">
         <f t="shared" si="14"/>
         <v>10495753.8623529</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <v>2178295.91129921</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="8">
         <v>1774037.17019853</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="8">
         <v>2402552.60023555</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="8">
         <v>4140868.18061964</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="8">
         <v>0</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="6">
         <v>44805</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="7">
         <f t="shared" si="15"/>
         <v>10495753.8623529</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="9">
         <f t="shared" ref="K21:O21" si="21">IFERROR(C21/$B21,0)</f>
         <v>0.207540681676283</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="9">
         <f t="shared" si="21"/>
         <v>0.169024273383716</v>
       </c>
-      <c r="M21" s="8">
+      <c r="M21" s="9">
         <f t="shared" si="21"/>
         <v>0.228907102028491</v>
       </c>
-      <c r="N21" s="8">
+      <c r="N21" s="9">
         <f t="shared" si="21"/>
         <v>0.39452794291151</v>
       </c>
-      <c r="O21" s="8">
+      <c r="O21" s="9">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="5">
+      <c r="A22" s="6">
         <v>44835</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="7">
         <f t="shared" si="14"/>
         <v>10942533.5923534</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="8">
         <v>2894310.36115145</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="8">
         <v>1319452.59017167</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="8">
         <v>1403062.74041794</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="8">
         <v>3803571.17049764</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="8">
         <v>1522136.73011474</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="6">
         <v>44835</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J22" s="7">
         <f t="shared" si="15"/>
         <v>10942533.5923534</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="9">
         <f t="shared" ref="K22:O22" si="22">IFERROR(C22/$B22,0)</f>
         <v>0.264500934516114</v>
       </c>
-      <c r="L22" s="8">
+      <c r="L22" s="9">
         <f t="shared" si="22"/>
         <v>0.120580172684477</v>
       </c>
-      <c r="M22" s="8">
+      <c r="M22" s="9">
         <f t="shared" si="22"/>
         <v>0.128221012855596</v>
       </c>
-      <c r="N22" s="8">
+      <c r="N22" s="9">
         <f t="shared" si="22"/>
         <v>0.347595110254498</v>
       </c>
-      <c r="O22" s="8">
+      <c r="O22" s="9">
         <f t="shared" si="22"/>
         <v>0.139102769689316</v>
       </c>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="5">
+      <c r="A23" s="6">
         <v>44866</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="7">
         <f t="shared" si="14"/>
         <v>13400858.3544945</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <v>3252521.61156486</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="8">
         <v>2422647.63887558</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="8">
         <v>937420.570062064</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="8">
         <v>4608061.33371539</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="8">
         <v>2180207.20027664</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="6">
         <v>44866</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="7">
         <f t="shared" si="15"/>
         <v>13400858.3544945</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="9">
         <f t="shared" ref="K23:O23" si="23">IFERROR(C23/$B23,0)</f>
         <v>0.24270994629788</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="9">
         <f t="shared" si="23"/>
         <v>0.180783019623743</v>
       </c>
-      <c r="M23" s="8">
+      <c r="M23" s="9">
         <f t="shared" si="23"/>
         <v>0.0699522780753563</v>
       </c>
-      <c r="N23" s="8">
+      <c r="N23" s="9">
         <f t="shared" si="23"/>
         <v>0.343863147555014</v>
       </c>
-      <c r="O23" s="8">
+      <c r="O23" s="9">
         <f t="shared" si="23"/>
         <v>0.162691608448008</v>
       </c>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="5">
+      <c r="A24" s="6">
         <v>44896</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="7">
         <f t="shared" si="14"/>
         <v>15258929.9142797</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="8">
         <v>2753173.18996686</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="8">
         <v>2952210.67099827</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="8">
         <v>1103806.59032509</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="8">
         <v>5142806.50268109</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="8">
         <v>3306932.96030836</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="6">
         <v>44896</v>
       </c>
-      <c r="J24" s="6">
+      <c r="J24" s="7">
         <f t="shared" si="15"/>
         <v>15258929.9142797</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="9">
         <f t="shared" ref="K24:O24" si="24">IFERROR(C24/$B24,0)</f>
         <v>0.180430292650494</v>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="9">
         <f t="shared" si="24"/>
         <v>0.193474292600002</v>
       </c>
-      <c r="M24" s="8">
+      <c r="M24" s="9">
         <f t="shared" si="24"/>
         <v>0.0723384009577317</v>
       </c>
-      <c r="N24" s="8">
+      <c r="N24" s="9">
         <f t="shared" si="24"/>
         <v>0.337035855828155</v>
       </c>
-      <c r="O24" s="8">
+      <c r="O24" s="9">
         <f t="shared" si="24"/>
         <v>0.216721157963617</v>
       </c>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="5">
+      <c r="A25" s="6">
         <v>44927</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="7">
         <f t="shared" si="14"/>
         <v>18276742.8233353</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="8">
         <v>3024628.88019842</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="8">
         <v>4530061.69930018</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="8">
         <v>1582011.76025868</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="8">
         <v>3437246.61087767</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="8">
         <v>5702793.87270037</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="6">
         <v>44927</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="7">
         <f t="shared" si="15"/>
         <v>18276742.8233353</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="9">
         <f t="shared" ref="K25:O25" si="25">IFERROR(C25/$B25,0)</f>
         <v>0.16549058601058</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="9">
         <f t="shared" si="25"/>
         <v>0.247859355635092</v>
       </c>
-      <c r="M25" s="8">
+      <c r="M25" s="9">
         <f t="shared" si="25"/>
         <v>0.0865587361791185</v>
       </c>
-      <c r="N25" s="8">
+      <c r="N25" s="9">
         <f t="shared" si="25"/>
         <v>0.188066694602119</v>
       </c>
-      <c r="O25" s="8">
+      <c r="O25" s="9">
         <f t="shared" si="25"/>
         <v>0.312024627573091</v>
       </c>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="5">
+      <c r="A26" s="6">
         <v>44958</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="7">
         <f t="shared" si="14"/>
         <v>18700339.3314802</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="8">
         <v>3526821.3583757</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="8">
         <v>3455629.48960056</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="8">
         <v>3856710.69037558</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="8">
         <v>2545359.54030062</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="8">
         <v>5315818.25282776</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="6">
         <v>44958</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="7">
         <f t="shared" si="15"/>
         <v>18700339.3314802</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="9">
         <f t="shared" ref="K26:O26" si="26">IFERROR(C26/$B26,0)</f>
         <v>0.188596650352683</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="9">
         <f t="shared" si="26"/>
         <v>0.184789667628295</v>
       </c>
-      <c r="M26" s="8">
+      <c r="M26" s="9">
         <f t="shared" si="26"/>
         <v>0.206237470989801</v>
       </c>
-      <c r="N26" s="8">
+      <c r="N26" s="9">
         <f t="shared" si="26"/>
         <v>0.136113013522474</v>
       </c>
-      <c r="O26" s="8">
+      <c r="O26" s="9">
         <f t="shared" si="26"/>
         <v>0.284263197506748</v>
       </c>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="9">
+      <c r="A27" s="10">
         <v>44986</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="7">
         <f t="shared" si="14"/>
         <v>25037698.0738126</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="8">
         <v>2727451.83093454</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="8">
         <v>5357501.09718857</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="8">
         <v>2403373.87904484</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="8">
         <v>6634496.15238364</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="8">
         <v>7914875.114261</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="10">
         <v>44986</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="7">
         <f t="shared" si="15"/>
         <v>25037698.0738126</v>
       </c>
-      <c r="K27" s="8">
+      <c r="K27" s="9">
         <f t="shared" ref="K27:O27" si="27">IFERROR(C27/$B27,0)</f>
         <v>0.108933809445815</v>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="9">
         <f t="shared" si="27"/>
         <v>0.213977382481183</v>
       </c>
-      <c r="M27" s="8">
+      <c r="M27" s="9">
         <f t="shared" si="27"/>
         <v>0.0959902093219414</v>
       </c>
-      <c r="N27" s="8">
+      <c r="N27" s="9">
         <f t="shared" si="27"/>
         <v>0.26498027625482</v>
       </c>
-      <c r="O27" s="8">
+      <c r="O27" s="9">
         <f t="shared" si="27"/>
         <v>0.316118322496241</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:G2">
-    <cfRule type="colorScale" priority="48">
+    <cfRule type="colorScale" priority="53">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9055,7 +9070,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:O2">
-    <cfRule type="colorScale" priority="24">
+    <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9067,7 +9082,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:G3">
-    <cfRule type="colorScale" priority="47">
+    <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9079,7 +9094,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:O3">
-    <cfRule type="colorScale" priority="23">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9091,7 +9106,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:G4">
-    <cfRule type="colorScale" priority="46">
+    <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9103,7 +9118,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:O4">
-    <cfRule type="colorScale" priority="22">
+    <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9115,7 +9130,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:G5">
-    <cfRule type="colorScale" priority="45">
+    <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9127,7 +9142,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:O5">
-    <cfRule type="colorScale" priority="21">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9139,7 +9154,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:G6">
-    <cfRule type="colorScale" priority="44">
+    <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9151,7 +9166,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:O6">
-    <cfRule type="colorScale" priority="20">
+    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9163,7 +9178,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:G7">
-    <cfRule type="colorScale" priority="43">
+    <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9175,7 +9190,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:O7">
-    <cfRule type="colorScale" priority="19">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9187,7 +9202,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:G8">
-    <cfRule type="colorScale" priority="42">
+    <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9199,7 +9214,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8:O8">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9211,7 +9226,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:G9">
-    <cfRule type="colorScale" priority="41">
+    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9223,7 +9238,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:O9">
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9235,7 +9250,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10:G10">
-    <cfRule type="colorScale" priority="40">
+    <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9247,7 +9262,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K10:O10">
-    <cfRule type="colorScale" priority="16">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9259,7 +9274,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:G11">
-    <cfRule type="colorScale" priority="39">
+    <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9271,7 +9286,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:O11">
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9283,7 +9298,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12:G12">
-    <cfRule type="colorScale" priority="38">
+    <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9295,7 +9310,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12:O12">
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9307,7 +9322,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:G13">
-    <cfRule type="colorScale" priority="37">
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9319,7 +9334,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:O13">
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9331,7 +9346,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:G16">
-    <cfRule type="colorScale" priority="36">
+    <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9343,7 +9358,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16:O16">
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9355,7 +9370,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:G17">
-    <cfRule type="colorScale" priority="35">
+    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9367,7 +9382,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17:O17">
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9379,7 +9394,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">
-    <cfRule type="colorScale" priority="34">
+    <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9391,7 +9406,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18:O18">
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9403,7 +9418,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19:G19">
-    <cfRule type="colorScale" priority="33">
+    <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9415,7 +9430,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19:O19">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9427,7 +9442,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20:G20">
-    <cfRule type="colorScale" priority="32">
+    <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9439,7 +9454,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K20:O20">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9451,7 +9466,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:G21">
-    <cfRule type="colorScale" priority="31">
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9463,7 +9478,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:O21">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9475,7 +9490,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:G22">
-    <cfRule type="colorScale" priority="30">
+    <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9487,7 +9502,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:O22">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9499,7 +9514,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C23:G23">
-    <cfRule type="colorScale" priority="29">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9511,7 +9526,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K23:O23">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9523,7 +9538,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:G24">
-    <cfRule type="colorScale" priority="28">
+    <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9535,7 +9550,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K24:O24">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9547,7 +9562,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:G25">
-    <cfRule type="colorScale" priority="27">
+    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9559,7 +9574,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:O25">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9571,7 +9586,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26:G26">
-    <cfRule type="colorScale" priority="26">
+    <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9583,7 +9598,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:O26">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9595,7 +9610,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C27:G27">
-    <cfRule type="colorScale" priority="25">
+    <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9607,7 +9622,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27:O27">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9618,9 +9633,65 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B13">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{aadf01bd-c3c6-4662-abb5-66d3fb8a6f7e}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:B27">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{ec26ac74-af8d-4960-b950-0a096c29c59a}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="1" scale="64" orientation="landscape" horizontalDpi="600"/>
   <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{aadf01bd-c3c6-4662-abb5-66d3fb8a6f7e}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B2:B13</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{ec26ac74-af8d-4960-b950-0a096c29c59a}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B16:B27</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>